--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0002T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.99372541792035</v>
+        <v>10.39898038041206</v>
       </c>
       <c r="D2" t="n">
-        <v>63.84878289072688</v>
+        <v>10.37542721974312</v>
       </c>
       <c r="E2" t="n">
-        <v>14.80935665760507</v>
+        <v>2.406520456860824</v>
       </c>
       <c r="F2" t="n">
-        <v>15.05290689860262</v>
+        <v>2.446097371022925</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.06393063347017</v>
+        <v>7.972888727938903</v>
       </c>
       <c r="D3" t="n">
-        <v>49.30941256928127</v>
+        <v>8.012779542508207</v>
       </c>
       <c r="E3" t="n">
-        <v>14.80935665760507</v>
+        <v>2.406520456860824</v>
       </c>
       <c r="F3" t="n">
-        <v>15.05290689860262</v>
+        <v>2.446097371022925</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.85729818137516</v>
+        <v>6.964310954473464</v>
       </c>
       <c r="D4" t="n">
-        <v>42.87458842854915</v>
+        <v>6.967120619639236</v>
       </c>
       <c r="E4" t="n">
-        <v>14.80935665760507</v>
+        <v>2.406520456860824</v>
       </c>
       <c r="F4" t="n">
-        <v>15.05290689860262</v>
+        <v>2.446097371022925</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.77395457177604</v>
+        <v>4.188267617913607</v>
       </c>
       <c r="D5" t="n">
-        <v>25.42797411352204</v>
+        <v>4.132045793447332</v>
       </c>
       <c r="E5" t="n">
-        <v>14.80935665760507</v>
+        <v>2.406520456860824</v>
       </c>
       <c r="F5" t="n">
-        <v>15.05290689860262</v>
+        <v>2.446097371022925</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.6319291344412</v>
+        <v>4.002688484346694</v>
       </c>
       <c r="D6" t="n">
-        <v>23.79975827447857</v>
+        <v>3.867460719602768</v>
       </c>
       <c r="E6" t="n">
-        <v>14.80935665760507</v>
+        <v>2.406520456860824</v>
       </c>
       <c r="F6" t="n">
-        <v>15.05290689860262</v>
+        <v>2.446097371022925</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
